--- a/inventories/optimized/lci-Salar-del-Hombre-Muerto-North.xlsx
+++ b/inventories/optimized/lci-Salar-del-Hombre-Muerto-North.xlsx
@@ -818,7 +818,7 @@
         <v>3</v>
       </c>
       <c r="B27">
-        <v>-0.007317182565765822</v>
+        <v>-0.007317182565765823</v>
       </c>
       <c r="C27" t="s">
         <v>1</v>
@@ -852,7 +852,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0.002031639510995661</v>
+        <v>0.00203163951099566</v>
       </c>
       <c r="C29" t="s">
         <v>1</v>
@@ -869,7 +869,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>0.0115235349695798</v>
+        <v>0.01152353496957979</v>
       </c>
       <c r="C30" t="s">
         <v>31</v>
@@ -886,7 +886,7 @@
         <v>32</v>
       </c>
       <c r="B31">
-        <v>0.02971318189354888</v>
+        <v>0.02971318189354889</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -920,7 +920,7 @@
         <v>35</v>
       </c>
       <c r="B33">
-        <v>0.0004456977284032336</v>
+        <v>0.0004456977284032337</v>
       </c>
       <c r="C33" t="s">
         <v>31</v>
@@ -937,7 +937,7 @@
         <v>36</v>
       </c>
       <c r="B34">
-        <v>-0.00835714606118099</v>
+        <v>-0.008357146061180988</v>
       </c>
       <c r="C34" t="s">
         <v>31</v>
@@ -1201,7 +1201,7 @@
         <v>3</v>
       </c>
       <c r="B60">
-        <v>0.1090671141925889</v>
+        <v>0.1061846590212545</v>
       </c>
       <c r="C60" t="s">
         <v>1</v>
@@ -1218,7 +1218,7 @@
         <v>41</v>
       </c>
       <c r="B61">
-        <v>0.8636661072592638</v>
+        <v>0.8672691762234319</v>
       </c>
       <c r="C61" t="s">
         <v>1</v>
@@ -1235,7 +1235,7 @@
         <v>28</v>
       </c>
       <c r="B62">
-        <v>0.2119427740406176</v>
+        <v>0.2128269634569984</v>
       </c>
       <c r="C62" t="s">
         <v>1</v>
@@ -1252,7 +1252,7 @@
         <v>42</v>
       </c>
       <c r="B63">
-        <v>0.02726677854814723</v>
+        <v>0.02654616475531363</v>
       </c>
       <c r="C63" t="s">
         <v>33</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="B75">
-        <v>0.0004885719404391602</v>
+        <v>0.0004885719404391603</v>
       </c>
       <c r="C75" t="s">
         <v>1</v>
@@ -1384,7 +1384,7 @@
         <v>44</v>
       </c>
       <c r="B76">
-        <v>0.9979905495778574</v>
+        <v>0.9979905495778575</v>
       </c>
       <c r="C76" t="s">
         <v>1</v>
@@ -1533,7 +1533,7 @@
         <v>3</v>
       </c>
       <c r="B90">
-        <v>0.004104901823987733</v>
+        <v>0.004104901823987732</v>
       </c>
       <c r="C90" t="s">
         <v>1</v>
@@ -1831,7 +1831,7 @@
         <v>40</v>
       </c>
       <c r="B118">
-        <v>35.07177092334429</v>
+        <v>36.0238181248672</v>
       </c>
       <c r="C118" t="s">
         <v>1</v>
@@ -1848,7 +1848,7 @@
         <v>22</v>
       </c>
       <c r="B119">
-        <v>0.03402485238831908</v>
+        <v>0.03494848027039355</v>
       </c>
       <c r="C119" t="s">
         <v>23</v>
@@ -1865,7 +1865,7 @@
         <v>49</v>
       </c>
       <c r="B120">
-        <v>-0.02399185040846099</v>
+        <v>-0.02462707802881201</v>
       </c>
       <c r="C120" t="s">
         <v>1</v>
@@ -1997,7 +1997,7 @@
         <v>22</v>
       </c>
       <c r="B133">
-        <v>0.0004736842105263158</v>
+        <v>0.0004736842105263159</v>
       </c>
       <c r="C133" t="s">
         <v>23</v>
@@ -2014,7 +2014,7 @@
         <v>36</v>
       </c>
       <c r="B134">
-        <v>-0.05263157894736842</v>
+        <v>-0.05263157894736843</v>
       </c>
       <c r="C134" t="s">
         <v>31</v>
@@ -2146,7 +2146,7 @@
         <v>22</v>
       </c>
       <c r="B147">
-        <v>3.187993818510205E-05</v>
+        <v>3.187993818510206E-05</v>
       </c>
       <c r="C147" t="s">
         <v>23</v>
@@ -2163,7 +2163,7 @@
         <v>36</v>
       </c>
       <c r="B148">
-        <v>-0.003542215353900227</v>
+        <v>-0.003542215353900229</v>
       </c>
       <c r="C148" t="s">
         <v>31</v>
@@ -2312,7 +2312,7 @@
         <v>36</v>
       </c>
       <c r="B162">
-        <v>-0.001951895743021925</v>
+        <v>-0.001951895743021924</v>
       </c>
       <c r="C162" t="s">
         <v>31</v>
@@ -2708,7 +2708,7 @@
         <v>54</v>
       </c>
       <c r="B201">
-        <v>0.01556736519116207</v>
+        <v>0.01509298129060795</v>
       </c>
       <c r="D201" t="s">
         <v>11</v>
@@ -2725,7 +2725,7 @@
         <v>55</v>
       </c>
       <c r="B202">
-        <v>1.277429310825838E-10</v>
+        <v>1.23850224181253E-10</v>
       </c>
       <c r="D202" t="s">
         <v>56</v>
@@ -2742,7 +2742,7 @@
         <v>58</v>
       </c>
       <c r="B203">
-        <v>4.258097702752791E-12</v>
+        <v>4.128340806041768E-12</v>
       </c>
       <c r="D203" t="s">
         <v>59</v>
@@ -2759,7 +2759,7 @@
         <v>60</v>
       </c>
       <c r="B204">
-        <v>4.258097702752791E-12</v>
+        <v>4.128340806041768E-12</v>
       </c>
       <c r="D204" t="s">
         <v>59</v>
@@ -2810,7 +2810,7 @@
         <v>3</v>
       </c>
       <c r="B207">
-        <v>0.9162896531155279</v>
+        <v>0.9188405562635018</v>
       </c>
       <c r="C207" t="s">
         <v>1</v>
@@ -2827,7 +2827,7 @@
         <v>61</v>
       </c>
       <c r="B208">
-        <v>5.215068060779234E-05</v>
+        <v>5.056149432100043E-05</v>
       </c>
       <c r="C208" t="s">
         <v>1</v>
@@ -2844,7 +2844,7 @@
         <v>22</v>
       </c>
       <c r="B209">
-        <v>0.003776681464439038</v>
+        <v>0.003666303140300071</v>
       </c>
       <c r="C209" t="s">
         <v>23</v>
@@ -2861,7 +2861,7 @@
         <v>45</v>
       </c>
       <c r="B210">
-        <v>6.136445536146954E-10</v>
+        <v>0.09485949867543304</v>
       </c>
       <c r="C210" t="s">
         <v>31</v>
@@ -2878,7 +2878,7 @@
         <v>63</v>
       </c>
       <c r="B211">
-        <v>0.001649321375253118</v>
+        <v>0.001599061649368095</v>
       </c>
       <c r="C211" t="s">
         <v>31</v>
@@ -2895,7 +2895,7 @@
         <v>64</v>
       </c>
       <c r="B212">
-        <v>-5.79218378021217</v>
+        <v>-5.615678719744823</v>
       </c>
       <c r="C212" t="s">
         <v>31</v>
@@ -2912,7 +2912,7 @@
         <v>49</v>
       </c>
       <c r="B213">
-        <v>-0.0009162896529183989</v>
+        <v>-0.0008883675829822749</v>
       </c>
       <c r="C213" t="s">
         <v>1</v>
